--- a/data/demo-backdated-2026-07-06.xlsx
+++ b/data/demo-backdated-2026-07-06.xlsx
@@ -615,7 +615,7 @@
       </c>
       <c r="O2" s="18" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:14</t>
+          <t>2026-08-01T21:43:12</t>
         </is>
       </c>
       <c r="P2" s="19" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="O3" s="18" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:14</t>
+          <t>2026-08-01T21:43:12</t>
         </is>
       </c>
       <c r="P3" s="19" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="O4" s="18" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:14</t>
+          <t>2026-08-01T21:43:12</t>
         </is>
       </c>
       <c r="P4" s="19" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="O5" s="18" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:14</t>
+          <t>2026-08-01T21:43:12</t>
         </is>
       </c>
       <c r="P5" s="19" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="O6" s="18" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:14</t>
+          <t>2026-08-01T21:43:12</t>
         </is>
       </c>
       <c r="P6" s="19" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="O7" s="18" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:14</t>
+          <t>2026-08-01T21:43:12</t>
         </is>
       </c>
       <c r="P7" s="19" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="O8" s="18" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:14</t>
+          <t>2026-08-01T21:43:12</t>
         </is>
       </c>
       <c r="P8" s="19" t="inlineStr">
@@ -28103,7 +28103,7 @@
       </c>
       <c r="O2" s="21" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:14</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P2" s="22" t="inlineStr">
@@ -28186,7 +28186,7 @@
       </c>
       <c r="O3" s="23" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:14</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P3" s="24" t="inlineStr">
@@ -28269,7 +28269,7 @@
       </c>
       <c r="O4" s="23" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:14</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P4" s="24" t="inlineStr">
@@ -28348,7 +28348,7 @@
       </c>
       <c r="O5" s="25" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:14</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P5" s="26" t="inlineStr">
@@ -28427,7 +28427,7 @@
       </c>
       <c r="O6" s="25" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:14</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P6" s="26" t="inlineStr">
@@ -28506,7 +28506,7 @@
       </c>
       <c r="O7" s="25" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:14</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P7" s="26" t="inlineStr">
@@ -28585,7 +28585,7 @@
       </c>
       <c r="O8" s="25" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:14</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P8" s="26" t="inlineStr">
@@ -28664,7 +28664,7 @@
       </c>
       <c r="O9" s="25" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:14</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P9" s="26" t="inlineStr">
@@ -28743,7 +28743,7 @@
       </c>
       <c r="O10" s="25" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:14</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P10" s="26" t="inlineStr">
@@ -28822,7 +28822,7 @@
       </c>
       <c r="O11" s="25" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:14</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P11" s="26" t="inlineStr">
@@ -28901,7 +28901,7 @@
       </c>
       <c r="O12" s="25" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:14</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P12" s="26" t="inlineStr">
@@ -28980,7 +28980,7 @@
       </c>
       <c r="O13" s="25" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:14</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P13" s="26" t="inlineStr">
@@ -29059,7 +29059,7 @@
       </c>
       <c r="O14" s="25" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:14</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P14" s="26" t="inlineStr">
@@ -29138,7 +29138,7 @@
       </c>
       <c r="O15" s="25" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:14</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P15" s="26" t="inlineStr">
@@ -29217,7 +29217,7 @@
       </c>
       <c r="O16" s="25" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:14</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P16" s="26" t="inlineStr">
@@ -29296,7 +29296,7 @@
       </c>
       <c r="O17" s="25" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:14</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P17" s="26" t="inlineStr">
